--- a/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:47</t>
+          <t>2026-09-01 03:16:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:48</t>
+          <t>2026-09-01 03:16:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:49</t>
+          <t>2026-09-01 03:16:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:51</t>
+          <t>2026-09-01 03:16:46</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5130</v>
+        <v>5410</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>16065</v>
+        <v>17120</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.55%182.5</t>
+          <t>-3.56%176</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>182.5</v>
+        <v>176</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:25</t>
+          <t>2026-09-01 15:29:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6100</v>
+        <v>5995</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,18 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.9%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
+          <t>+6.72%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>874</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1452,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,18 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.56%6285</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.56%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>6910</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1515,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,18 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.54%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5885</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1578,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,18 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.55%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1840</t>
-        </is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1865</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1641,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,18 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.98%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
+          <t>+6.68%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2315</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1704,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,18 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.77%129</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+          <t>+2.71%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>132.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1767,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>202609TX台指期貨</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5870</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.71%19</t>
+          <t>1.48%26,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>26000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>5289宜鼎國際</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>0%1450</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.71%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>5860</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1450</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.48%26,000</t>
+          <t>1.34%94,872</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>26000</v>
+        <v>94872</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5289宜鼎國際</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.36%1450</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.36%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
+          <t>+4.22%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>568</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.34%94,872</t>
+          <t>1.29%243,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>94872</v>
+        <v>243000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,40 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-8.71%545</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.71%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
+          <t>+4.45%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>610</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.29%243,000</t>
+          <t>1.13%200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>243000</v>
+        <v>200000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,40 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.96%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
+          <t>-2.97%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3425</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.13%200,000</t>
+          <t>0.86%25,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>200000</v>
+        <v>25000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,40 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-1.85%2125</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+6.81%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3530</t>
-        </is>
+          <t>-1.85%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2125</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.86%25,000</t>
+          <t>0.76%36,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>25000</v>
+        <v>36000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,40 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-2.78%122.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.7%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
+          <t>-2.78%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>122.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.76%36,000</t>
+          <t>0.54%444,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>36000</v>
+        <v>444000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>2301光寶科技</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.4%126</t>
+          <t>-1.48%300.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+          <t>-1.48%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>300.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.54%444,000</t>
+          <t>0.52%175,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>444000</v>
+        <v>175000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:26</t>
+          <t>2026-09-01 15:29:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,27 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2301光寶科技</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-3.94%305</t>
+          <t>+9.85%524</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.94%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+          <t>+9.85%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>524</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.52%175,000</t>
+          <t>0.52%113,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2330,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>175000</v>
+        <v>113000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2351,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2364,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.91%477</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>477</v>
+        <v>1375</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.52%113,000</t>
+          <t>0.50%38,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>113000</v>
+        <v>38000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2412,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2425,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.47%1345</t>
+          <t>+1.79%624</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1345</v>
+        <v>624</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.50%38,000</t>
+          <t>0.49%82,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>38000</v>
+        <v>82000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2473,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2486,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.49%613</t>
+          <t>+1.99%66.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>613</v>
+        <v>66.7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.49%82,000</t>
+          <t>0.49%773,360</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>82000</v>
+        <v>773360</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2534,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2547,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>2347聯強</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.19%65.4</t>
+          <t>-1.15%86</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>65.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.49%773,360</t>
+          <t>0.48%567,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>773360</v>
+        <v>567000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2595,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2613,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.36%33.85</t>
+          <t>+3.25%34.95</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>33.85</v>
+        <v>34.95</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2656,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2669,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>2368金像電子</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.58%87</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>87</v>
+        <v>1225</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.48%567,000</t>
+          <t>0.46%41,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>567000</v>
+        <v>41000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2717,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2730,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2368金像電子</t>
+          <t>8358金居開發</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.1%1165</t>
+          <t>-2.59%526</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1165</v>
+        <v>526</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.46%41,000</t>
+          <t>0.46%87,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2757,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>41000</v>
+        <v>87000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2778,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2791,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8358金居開發</t>
+          <t>2890永豐金控</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.55%540</t>
+          <t>+0.97%41.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>540</v>
+        <v>41.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.46%87,000</t>
+          <t>0.45%1,134,220</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>87000</v>
+        <v>1134220</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2839,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2852,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2890永豐金控</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.27%41.1</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.27%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>41.1</v>
+        <v>182</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.45%1,134,220</t>
+          <t>0.45%260,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2879,7 +2849,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1134220</v>
+        <v>260000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2900,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2913,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>+4.17%237.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>178</v>
+        <v>237.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.45%260,000</t>
+          <t>0.43%195,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>260000</v>
+        <v>195000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2961,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2974,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.98%228</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>228</v>
+        <v>1480</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.43%195,000</t>
+          <t>0.43%32,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3001,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>195000</v>
+        <v>32000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3022,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3035,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-8.61%1380</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.61%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1380</v>
+        <v>2030</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.43%32,000</t>
+          <t>0.42%22,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>32000</v>
+        <v>22000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3083,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3096,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+6.04%667</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+6.04%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1960</v>
+        <v>667</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.42%22,000</t>
+          <t>0.40%65,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>22000</v>
+        <v>65000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3144,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3157,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-7.77%629</t>
+          <t>+5.02%711</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-7.77%</t>
+          <t>+5.02%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>629</v>
+        <v>711</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.40%65,000</t>
+          <t>0.39%59,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>65000</v>
+        <v>59000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3205,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:27</t>
+          <t>2026-09-01 15:29:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3223,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3249,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3266,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:29</t>
+          <t>2026-09-01 15:29:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3279,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.2%677</t>
+          <t>+8.93%744</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+8.93%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>677</v>
+        <v>744</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.39%59,000</t>
+          <t>0.38%57,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>59000</v>
+        <v>57000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3327,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:29</t>
+          <t>2026-09-01 15:29:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3340,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>+4.54%507</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+4.54%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>683</v>
+        <v>507</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.38%57,000</t>
+          <t>0.37%79,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>57000</v>
+        <v>79000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3388,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:29</t>
+          <t>2026-09-01 15:29:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3401,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6139亞翔工程</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.52%485</t>
+          <t>+1.99%770</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>485</v>
+        <v>770</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.37%79,000</t>
+          <t>0.35%48,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>79000</v>
+        <v>48000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3449,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:29</t>
+          <t>2026-09-01 15:29:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3467,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-5.84%548</t>
+          <t>+0.36%550</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.84%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3493,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3510,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:29</t>
+          <t>2026-09-01 15:29:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3523,102 +3493,41 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6139亞翔工程</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.58%755</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>755</v>
+        <v>4275</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.35%48,000</t>
+          <t>0.32%8,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>48000</v>
+        <v>8000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-01 03:33:29</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3661世芯-KY</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>+0.25%4075</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>+0.25%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>4075</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0.32%8,000</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:51</t>
+          <t>2026-09-01 17:55:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:53</t>
+          <t>2026-09-01 17:55:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:54</t>
+          <t>2026-09-01 17:55:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:55</t>
+          <t>2026-09-01 17:55:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:55</t>
+          <t>2026-09-01 17:55:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:55</t>
+          <t>2026-09-01 17:55:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:55</t>
+          <t>2026-09-01 17:55:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:55</t>
+          <t>2026-09-01 17:55:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:37</t>
+          <t>2026-09-01 20:36:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:38</t>
+          <t>2026-09-01 20:36:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:40</t>
+          <t>2026-09-01 20:36:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:41</t>
+          <t>2026-09-01 20:36:27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:41</t>
+          <t>2026-09-01 20:36:27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:41</t>
+          <t>2026-09-01 20:36:27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:41</t>
+          <t>2026-09-01 20:36:27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:41</t>
+          <t>2026-09-01 20:36:27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
